--- a/04_excel_func/Кейс №4 "Excel и необычные задачи от студентов".xlsx
+++ b/04_excel_func/Кейс №4 "Excel и необычные задачи от студентов".xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pyshkovni/РАНХиГС.Диск/Материал/economic-informatics/04_excel_func/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31803D0B-E8C8-A84E-A179-219B2F095456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5765B42F-05F6-5B40-A0EE-FA1C43C2A4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="640" yWindow="1040" windowWidth="27840" windowHeight="16340" xr2:uid="{8102696D-405D-E342-B207-5311608B1291}"/>
   </bookViews>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="501">
   <si>
     <t>Фамилия</t>
   </si>
@@ -1635,13 +1635,19 @@
   </si>
   <si>
     <t>Хороших Харитон Харитонович</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1686,13 +1692,6 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2263,10 +2262,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2291,20 +2290,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2323,7 +2322,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2333,107 +2332,98 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="20" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="20" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="19" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="19" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -3878,8 +3868,8 @@
       <c r="B3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="4">
-        <v>1</v>
+      <c r="C3" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D3" s="12"/>
     </row>
@@ -3890,8 +3880,8 @@
       <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="4">
-        <v>1</v>
+      <c r="C4" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D4" s="12"/>
     </row>
@@ -3902,8 +3892,8 @@
       <c r="B5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="4">
-        <v>2</v>
+      <c r="C5" s="4" t="s">
+        <v>500</v>
       </c>
       <c r="D5" s="12"/>
     </row>
@@ -3914,8 +3904,8 @@
       <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="4">
-        <v>1</v>
+      <c r="C6" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D6" s="12"/>
     </row>
@@ -3926,8 +3916,8 @@
       <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="4">
-        <v>1</v>
+      <c r="C7" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D7" s="12"/>
     </row>
@@ -3938,8 +3928,8 @@
       <c r="B8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="4">
-        <v>1</v>
+      <c r="C8" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D8" s="12"/>
     </row>
@@ -3950,8 +3940,8 @@
       <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="4">
-        <v>2</v>
+      <c r="C9" s="4" t="s">
+        <v>500</v>
       </c>
       <c r="D9" s="12"/>
     </row>
@@ -3962,8 +3952,8 @@
       <c r="B10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="4">
-        <v>1</v>
+      <c r="C10" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D10" s="12"/>
     </row>
@@ -3974,8 +3964,8 @@
       <c r="B11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="4">
-        <v>1</v>
+      <c r="C11" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D11" s="12"/>
     </row>
@@ -3986,8 +3976,8 @@
       <c r="B12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="4">
-        <v>1</v>
+      <c r="C12" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D12" s="12"/>
     </row>
@@ -3998,8 +3988,8 @@
       <c r="B13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="4">
-        <v>1</v>
+      <c r="C13" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D13" s="12"/>
     </row>
@@ -4010,8 +4000,8 @@
       <c r="B14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="4">
-        <v>2</v>
+      <c r="C14" s="4" t="s">
+        <v>500</v>
       </c>
       <c r="D14" s="12"/>
     </row>
@@ -4022,8 +4012,8 @@
       <c r="B15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="4">
-        <v>2</v>
+      <c r="C15" s="4" t="s">
+        <v>500</v>
       </c>
       <c r="D15" s="12"/>
     </row>
@@ -4034,8 +4024,8 @@
       <c r="B16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="4">
-        <v>2</v>
+      <c r="C16" s="4" t="s">
+        <v>500</v>
       </c>
       <c r="D16" s="12"/>
     </row>
@@ -4046,8 +4036,8 @@
       <c r="B17" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="4">
-        <v>2</v>
+      <c r="C17" s="4" t="s">
+        <v>500</v>
       </c>
       <c r="D17" s="12"/>
     </row>
@@ -4058,8 +4048,8 @@
       <c r="B18" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="4">
-        <v>2</v>
+      <c r="C18" s="4" t="s">
+        <v>500</v>
       </c>
       <c r="D18" s="12"/>
     </row>
@@ -4070,8 +4060,8 @@
       <c r="B19" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="4">
-        <v>1</v>
+      <c r="C19" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D19" s="12"/>
     </row>
@@ -4082,8 +4072,8 @@
       <c r="B20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="4">
-        <v>2</v>
+      <c r="C20" s="4" t="s">
+        <v>500</v>
       </c>
       <c r="D20" s="12"/>
     </row>
@@ -4094,8 +4084,8 @@
       <c r="B21" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="4">
-        <v>1</v>
+      <c r="C21" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D21" s="12"/>
     </row>
@@ -4106,8 +4096,8 @@
       <c r="B22" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="4">
-        <v>2</v>
+      <c r="C22" s="4" t="s">
+        <v>500</v>
       </c>
       <c r="D22" s="12"/>
     </row>
@@ -4118,8 +4108,8 @@
       <c r="B23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="4">
-        <v>2</v>
+      <c r="C23" s="4" t="s">
+        <v>500</v>
       </c>
       <c r="D23" s="12"/>
     </row>
@@ -4130,8 +4120,8 @@
       <c r="B24" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="4">
-        <v>1</v>
+      <c r="C24" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D24" s="12"/>
     </row>
@@ -4142,8 +4132,8 @@
       <c r="B25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="4">
-        <v>1</v>
+      <c r="C25" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D25" s="12"/>
     </row>
@@ -4154,8 +4144,8 @@
       <c r="B26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="4">
-        <v>1</v>
+      <c r="C26" s="4" t="s">
+        <v>499</v>
       </c>
       <c r="D26" s="12"/>
     </row>
@@ -4166,8 +4156,8 @@
       <c r="B27" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="4">
-        <v>2</v>
+      <c r="C27" s="4" t="s">
+        <v>500</v>
       </c>
       <c r="D27" s="12"/>
     </row>
@@ -4178,8 +4168,8 @@
       <c r="B28" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="6">
-        <v>1</v>
+      <c r="C28" s="6" t="s">
+        <v>499</v>
       </c>
       <c r="D28" s="13"/>
     </row>
@@ -4208,24 +4198,24 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="77" t="s">
+      <c r="E2" s="70" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="71" t="s">
         <v>58</v>
       </c>
       <c r="B3" s="24"/>
@@ -4234,7 +4224,7 @@
       <c r="E3" s="25"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="72" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="24"/>
@@ -4243,7 +4233,7 @@
       <c r="E4" s="25"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="73" t="s">
         <v>59</v>
       </c>
       <c r="B5" s="24"/>
@@ -4252,7 +4242,7 @@
       <c r="E5" s="25"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="73" t="s">
         <v>60</v>
       </c>
       <c r="B6" s="24"/>
@@ -4261,7 +4251,7 @@
       <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="73" t="s">
         <v>61</v>
       </c>
       <c r="B7" s="24"/>
@@ -4270,7 +4260,7 @@
       <c r="E7" s="25"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="74" t="s">
         <v>62</v>
       </c>
       <c r="B8" s="26"/>
@@ -4302,31 +4292,31 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="C2" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="83" t="s">
+      <c r="D2" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="83" t="s">
+      <c r="E2" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="G2" s="84" t="s">
+      <c r="G2" s="77" t="s">
         <v>341</v>
       </c>
-      <c r="H2" s="84" t="s">
+      <c r="H2" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="I2" s="84" t="s">
+      <c r="I2" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="J2" s="83" t="s">
+      <c r="J2" s="76" t="s">
         <v>92</v>
       </c>
     </row>
@@ -4343,13 +4333,13 @@
       <c r="D3" s="44">
         <v>44378</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="4">
         <v>52</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="G3" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="48" t="s">
         <v>160</v>
       </c>
       <c r="I3" s="5"/>
@@ -4368,13 +4358,13 @@
       <c r="D4" s="44">
         <v>44379</v>
       </c>
-      <c r="E4" s="45">
+      <c r="E4" s="4">
         <v>57</v>
       </c>
-      <c r="G4" s="51" t="s">
+      <c r="G4" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="49" t="s">
         <v>142</v>
       </c>
       <c r="I4" s="4"/>
@@ -4387,19 +4377,19 @@
       <c r="B5" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="45" t="s">
         <v>101</v>
       </c>
       <c r="D5" s="44">
         <v>44380</v>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="4">
         <v>6</v>
       </c>
-      <c r="G5" s="51" t="s">
+      <c r="G5" s="49" t="s">
         <v>267</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="H5" s="49" t="s">
         <v>268</v>
       </c>
       <c r="I5" s="4"/>
@@ -4418,13 +4408,13 @@
       <c r="D6" s="44">
         <v>44378</v>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="4">
         <v>48</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="H6" s="52" t="s">
+      <c r="H6" s="50" t="s">
         <v>164</v>
       </c>
       <c r="I6" s="6"/>
@@ -4437,13 +4427,13 @@
       <c r="B7" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="45" t="s">
         <v>107</v>
       </c>
       <c r="D7" s="44">
         <v>44380</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="4">
         <v>69</v>
       </c>
     </row>
@@ -4460,7 +4450,7 @@
       <c r="D8" s="44">
         <v>44378</v>
       </c>
-      <c r="E8" s="45">
+      <c r="E8" s="4">
         <v>82</v>
       </c>
     </row>
@@ -4477,7 +4467,7 @@
       <c r="D9" s="44">
         <v>44380</v>
       </c>
-      <c r="E9" s="45">
+      <c r="E9" s="4">
         <v>74</v>
       </c>
     </row>
@@ -4494,7 +4484,7 @@
       <c r="D10" s="44">
         <v>44378</v>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="4">
         <v>37</v>
       </c>
     </row>
@@ -4511,7 +4501,7 @@
       <c r="D11" s="44">
         <v>44380</v>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="4">
         <v>60</v>
       </c>
     </row>
@@ -4522,13 +4512,13 @@
       <c r="B12" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="45" t="s">
         <v>122</v>
       </c>
       <c r="D12" s="44">
         <v>44380</v>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="4">
         <v>90</v>
       </c>
     </row>
@@ -4545,7 +4535,7 @@
       <c r="D13" s="44">
         <v>44380</v>
       </c>
-      <c r="E13" s="45">
+      <c r="E13" s="4">
         <v>34</v>
       </c>
     </row>
@@ -4562,7 +4552,7 @@
       <c r="D14" s="44">
         <v>44381</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="4">
         <v>83</v>
       </c>
     </row>
@@ -4573,13 +4563,13 @@
       <c r="B15" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="46" t="s">
+      <c r="C15" s="45" t="s">
         <v>122</v>
       </c>
       <c r="D15" s="44">
         <v>44383</v>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="4">
         <v>23</v>
       </c>
     </row>
@@ -4590,13 +4580,13 @@
       <c r="B16" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="45" t="s">
         <v>122</v>
       </c>
       <c r="D16" s="44">
         <v>44383</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="4">
         <v>53</v>
       </c>
     </row>
@@ -4607,13 +4597,13 @@
       <c r="B17" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="45" t="s">
         <v>122</v>
       </c>
       <c r="D17" s="44">
         <v>44382</v>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="4">
         <v>11</v>
       </c>
     </row>
@@ -4624,13 +4614,13 @@
       <c r="B18" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="45" t="s">
         <v>122</v>
       </c>
       <c r="D18" s="44">
         <v>44378</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="4">
         <v>96</v>
       </c>
     </row>
@@ -4641,13 +4631,13 @@
       <c r="B19" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="45" t="s">
         <v>122</v>
       </c>
       <c r="D19" s="44">
         <v>44378</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="4">
         <v>3</v>
       </c>
     </row>
@@ -4664,7 +4654,7 @@
       <c r="D20" s="44">
         <v>44378</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="4">
         <v>10</v>
       </c>
     </row>
@@ -4681,7 +4671,7 @@
       <c r="D21" s="44">
         <v>44378</v>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="4">
         <v>94</v>
       </c>
     </row>
@@ -4698,7 +4688,7 @@
       <c r="D22" s="44">
         <v>44378</v>
       </c>
-      <c r="E22" s="45">
+      <c r="E22" s="4">
         <v>49</v>
       </c>
     </row>
@@ -4709,13 +4699,13 @@
       <c r="B23" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="45" t="s">
         <v>122</v>
       </c>
       <c r="D23" s="44">
         <v>44382</v>
       </c>
-      <c r="E23" s="45">
+      <c r="E23" s="4">
         <v>90</v>
       </c>
     </row>
@@ -4726,13 +4716,13 @@
       <c r="B24" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="45" t="s">
         <v>122</v>
       </c>
       <c r="D24" s="44">
         <v>44384</v>
       </c>
-      <c r="E24" s="45">
+      <c r="E24" s="4">
         <v>64</v>
       </c>
     </row>
@@ -4749,7 +4739,7 @@
       <c r="D25" s="44">
         <v>44384</v>
       </c>
-      <c r="E25" s="45">
+      <c r="E25" s="4">
         <v>66</v>
       </c>
     </row>
@@ -4766,7 +4756,7 @@
       <c r="D26" s="44">
         <v>44381</v>
       </c>
-      <c r="E26" s="45">
+      <c r="E26" s="4">
         <v>77</v>
       </c>
     </row>
@@ -4783,7 +4773,7 @@
       <c r="D27" s="44">
         <v>44379</v>
       </c>
-      <c r="E27" s="45">
+      <c r="E27" s="4">
         <v>81</v>
       </c>
     </row>
@@ -4800,7 +4790,7 @@
       <c r="D28" s="44">
         <v>44381</v>
       </c>
-      <c r="E28" s="45">
+      <c r="E28" s="4">
         <v>44</v>
       </c>
     </row>
@@ -4817,7 +4807,7 @@
       <c r="D29" s="44">
         <v>44381</v>
       </c>
-      <c r="E29" s="45">
+      <c r="E29" s="4">
         <v>43</v>
       </c>
     </row>
@@ -4834,7 +4824,7 @@
       <c r="D30" s="44">
         <v>44381</v>
       </c>
-      <c r="E30" s="45">
+      <c r="E30" s="4">
         <v>25</v>
       </c>
     </row>
@@ -4851,7 +4841,7 @@
       <c r="D31" s="44">
         <v>44379</v>
       </c>
-      <c r="E31" s="45">
+      <c r="E31" s="4">
         <v>22</v>
       </c>
     </row>
@@ -4868,7 +4858,7 @@
       <c r="D32" s="44">
         <v>44384</v>
       </c>
-      <c r="E32" s="45">
+      <c r="E32" s="4">
         <v>38</v>
       </c>
     </row>
@@ -4885,7 +4875,7 @@
       <c r="D33" s="44">
         <v>44379</v>
       </c>
-      <c r="E33" s="45">
+      <c r="E33" s="4">
         <v>26</v>
       </c>
     </row>
@@ -4902,7 +4892,7 @@
       <c r="D34" s="44">
         <v>44384</v>
       </c>
-      <c r="E34" s="45">
+      <c r="E34" s="4">
         <v>45</v>
       </c>
     </row>
@@ -4919,7 +4909,7 @@
       <c r="D35" s="44">
         <v>44382</v>
       </c>
-      <c r="E35" s="45">
+      <c r="E35" s="4">
         <v>24</v>
       </c>
     </row>
@@ -4936,7 +4926,7 @@
       <c r="D36" s="44">
         <v>44379</v>
       </c>
-      <c r="E36" s="45">
+      <c r="E36" s="4">
         <v>51</v>
       </c>
     </row>
@@ -4953,7 +4943,7 @@
       <c r="D37" s="44">
         <v>44380</v>
       </c>
-      <c r="E37" s="45">
+      <c r="E37" s="4">
         <v>24</v>
       </c>
     </row>
@@ -4970,7 +4960,7 @@
       <c r="D38" s="44">
         <v>44380</v>
       </c>
-      <c r="E38" s="45">
+      <c r="E38" s="4">
         <v>2</v>
       </c>
     </row>
@@ -4987,7 +4977,7 @@
       <c r="D39" s="44">
         <v>44380</v>
       </c>
-      <c r="E39" s="45">
+      <c r="E39" s="4">
         <v>56</v>
       </c>
     </row>
@@ -5004,7 +4994,7 @@
       <c r="D40" s="44">
         <v>44379</v>
       </c>
-      <c r="E40" s="45">
+      <c r="E40" s="4">
         <v>93</v>
       </c>
     </row>
@@ -5021,7 +5011,7 @@
       <c r="D41" s="44">
         <v>44379</v>
       </c>
-      <c r="E41" s="45">
+      <c r="E41" s="4">
         <v>26</v>
       </c>
     </row>
@@ -5038,7 +5028,7 @@
       <c r="D42" s="44">
         <v>44383</v>
       </c>
-      <c r="E42" s="45">
+      <c r="E42" s="4">
         <v>51</v>
       </c>
     </row>
@@ -5055,7 +5045,7 @@
       <c r="D43" s="44">
         <v>44379</v>
       </c>
-      <c r="E43" s="45">
+      <c r="E43" s="4">
         <v>83</v>
       </c>
     </row>
@@ -5072,7 +5062,7 @@
       <c r="D44" s="44">
         <v>44381</v>
       </c>
-      <c r="E44" s="45">
+      <c r="E44" s="4">
         <v>61</v>
       </c>
     </row>
@@ -5089,7 +5079,7 @@
       <c r="D45" s="44">
         <v>44382</v>
       </c>
-      <c r="E45" s="45">
+      <c r="E45" s="4">
         <v>66</v>
       </c>
     </row>
@@ -5106,7 +5096,7 @@
       <c r="D46" s="44">
         <v>44382</v>
       </c>
-      <c r="E46" s="45">
+      <c r="E46" s="4">
         <v>26</v>
       </c>
     </row>
@@ -5123,7 +5113,7 @@
       <c r="D47" s="44">
         <v>44380</v>
       </c>
-      <c r="E47" s="45">
+      <c r="E47" s="4">
         <v>50</v>
       </c>
     </row>
@@ -5140,7 +5130,7 @@
       <c r="D48" s="44">
         <v>44380</v>
       </c>
-      <c r="E48" s="45">
+      <c r="E48" s="4">
         <v>95</v>
       </c>
     </row>
@@ -5157,7 +5147,7 @@
       <c r="D49" s="44">
         <v>44380</v>
       </c>
-      <c r="E49" s="45">
+      <c r="E49" s="4">
         <v>14</v>
       </c>
     </row>
@@ -5174,7 +5164,7 @@
       <c r="D50" s="44">
         <v>44378</v>
       </c>
-      <c r="E50" s="45">
+      <c r="E50" s="4">
         <v>55</v>
       </c>
     </row>
@@ -5191,7 +5181,7 @@
       <c r="D51" s="44">
         <v>44378</v>
       </c>
-      <c r="E51" s="45">
+      <c r="E51" s="4">
         <v>79</v>
       </c>
     </row>
@@ -5208,7 +5198,7 @@
       <c r="D52" s="44">
         <v>44378</v>
       </c>
-      <c r="E52" s="45">
+      <c r="E52" s="4">
         <v>3</v>
       </c>
     </row>
@@ -5225,7 +5215,7 @@
       <c r="D53" s="44">
         <v>44382</v>
       </c>
-      <c r="E53" s="45">
+      <c r="E53" s="4">
         <v>96</v>
       </c>
     </row>
@@ -5242,7 +5232,7 @@
       <c r="D54" s="44">
         <v>44383</v>
       </c>
-      <c r="E54" s="45">
+      <c r="E54" s="4">
         <v>29</v>
       </c>
     </row>
@@ -5259,7 +5249,7 @@
       <c r="D55" s="44">
         <v>44381</v>
       </c>
-      <c r="E55" s="45">
+      <c r="E55" s="4">
         <v>71</v>
       </c>
     </row>
@@ -5276,7 +5266,7 @@
       <c r="D56" s="44">
         <v>44380</v>
       </c>
-      <c r="E56" s="45">
+      <c r="E56" s="4">
         <v>39</v>
       </c>
     </row>
@@ -5293,7 +5283,7 @@
       <c r="D57" s="44">
         <v>44382</v>
       </c>
-      <c r="E57" s="45">
+      <c r="E57" s="4">
         <v>51</v>
       </c>
     </row>
@@ -5310,7 +5300,7 @@
       <c r="D58" s="44">
         <v>44383</v>
       </c>
-      <c r="E58" s="45">
+      <c r="E58" s="4">
         <v>83</v>
       </c>
     </row>
@@ -5327,7 +5317,7 @@
       <c r="D59" s="44">
         <v>44380</v>
       </c>
-      <c r="E59" s="45">
+      <c r="E59" s="4">
         <v>53</v>
       </c>
     </row>
@@ -5344,7 +5334,7 @@
       <c r="D60" s="44">
         <v>44384</v>
       </c>
-      <c r="E60" s="45">
+      <c r="E60" s="4">
         <v>85</v>
       </c>
     </row>
@@ -5355,13 +5345,13 @@
       <c r="B61" s="43" t="s">
         <v>216</v>
       </c>
-      <c r="C61" s="46" t="s">
+      <c r="C61" s="45" t="s">
         <v>217</v>
       </c>
       <c r="D61" s="44">
         <v>44378</v>
       </c>
-      <c r="E61" s="45">
+      <c r="E61" s="4">
         <v>15</v>
       </c>
     </row>
@@ -5378,7 +5368,7 @@
       <c r="D62" s="44">
         <v>44378</v>
       </c>
-      <c r="E62" s="45">
+      <c r="E62" s="4">
         <v>74</v>
       </c>
     </row>
@@ -5395,7 +5385,7 @@
       <c r="D63" s="44">
         <v>44378</v>
       </c>
-      <c r="E63" s="45">
+      <c r="E63" s="4">
         <v>90</v>
       </c>
     </row>
@@ -5412,7 +5402,7 @@
       <c r="D64" s="44">
         <v>44378</v>
       </c>
-      <c r="E64" s="45">
+      <c r="E64" s="4">
         <v>33</v>
       </c>
     </row>
@@ -5429,7 +5419,7 @@
       <c r="D65" s="44">
         <v>44378</v>
       </c>
-      <c r="E65" s="45">
+      <c r="E65" s="4">
         <v>16</v>
       </c>
     </row>
@@ -5446,7 +5436,7 @@
       <c r="D66" s="44">
         <v>44380</v>
       </c>
-      <c r="E66" s="45">
+      <c r="E66" s="4">
         <v>85</v>
       </c>
     </row>
@@ -5463,7 +5453,7 @@
       <c r="D67" s="44">
         <v>44384</v>
       </c>
-      <c r="E67" s="45">
+      <c r="E67" s="4">
         <v>57</v>
       </c>
     </row>
@@ -5480,7 +5470,7 @@
       <c r="D68" s="44">
         <v>44384</v>
       </c>
-      <c r="E68" s="45">
+      <c r="E68" s="4">
         <v>80</v>
       </c>
     </row>
@@ -5497,7 +5487,7 @@
       <c r="D69" s="44">
         <v>44381</v>
       </c>
-      <c r="E69" s="45">
+      <c r="E69" s="4">
         <v>42</v>
       </c>
     </row>
@@ -5514,7 +5504,7 @@
       <c r="D70" s="44">
         <v>44381</v>
       </c>
-      <c r="E70" s="45">
+      <c r="E70" s="4">
         <v>67</v>
       </c>
     </row>
@@ -5531,7 +5521,7 @@
       <c r="D71" s="44">
         <v>44382</v>
       </c>
-      <c r="E71" s="45">
+      <c r="E71" s="4">
         <v>32</v>
       </c>
     </row>
@@ -5548,7 +5538,7 @@
       <c r="D72" s="44">
         <v>44378</v>
       </c>
-      <c r="E72" s="45">
+      <c r="E72" s="4">
         <v>63</v>
       </c>
     </row>
@@ -5565,7 +5555,7 @@
       <c r="D73" s="44">
         <v>44383</v>
       </c>
-      <c r="E73" s="45">
+      <c r="E73" s="4">
         <v>68</v>
       </c>
     </row>
@@ -5582,7 +5572,7 @@
       <c r="D74" s="44">
         <v>44383</v>
       </c>
-      <c r="E74" s="45">
+      <c r="E74" s="4">
         <v>73</v>
       </c>
     </row>
@@ -5599,7 +5589,7 @@
       <c r="D75" s="44">
         <v>44378</v>
       </c>
-      <c r="E75" s="45">
+      <c r="E75" s="4">
         <v>19</v>
       </c>
     </row>
@@ -5616,7 +5606,7 @@
       <c r="D76" s="44">
         <v>44378</v>
       </c>
-      <c r="E76" s="45">
+      <c r="E76" s="4">
         <v>88</v>
       </c>
     </row>
@@ -5633,7 +5623,7 @@
       <c r="D77" s="44">
         <v>44378</v>
       </c>
-      <c r="E77" s="45">
+      <c r="E77" s="4">
         <v>89</v>
       </c>
     </row>
@@ -5650,7 +5640,7 @@
       <c r="D78" s="44">
         <v>44378</v>
       </c>
-      <c r="E78" s="45">
+      <c r="E78" s="4">
         <v>4</v>
       </c>
     </row>
@@ -5667,7 +5657,7 @@
       <c r="D79" s="44">
         <v>44381</v>
       </c>
-      <c r="E79" s="45">
+      <c r="E79" s="4">
         <v>38</v>
       </c>
     </row>
@@ -5684,7 +5674,7 @@
       <c r="D80" s="44">
         <v>44384</v>
       </c>
-      <c r="E80" s="45">
+      <c r="E80" s="4">
         <v>2</v>
       </c>
     </row>
@@ -5701,7 +5691,7 @@
       <c r="D81" s="44">
         <v>44380</v>
       </c>
-      <c r="E81" s="45">
+      <c r="E81" s="4">
         <v>98</v>
       </c>
     </row>
@@ -5712,13 +5702,13 @@
       <c r="B82" s="43" t="s">
         <v>279</v>
       </c>
-      <c r="C82" s="46" t="s">
+      <c r="C82" s="45" t="s">
         <v>280</v>
       </c>
       <c r="D82" s="44">
         <v>44378</v>
       </c>
-      <c r="E82" s="45">
+      <c r="E82" s="4">
         <v>74</v>
       </c>
     </row>
@@ -5735,7 +5725,7 @@
       <c r="D83" s="44">
         <v>44380</v>
       </c>
-      <c r="E83" s="45">
+      <c r="E83" s="4">
         <v>24</v>
       </c>
     </row>
@@ -5752,7 +5742,7 @@
       <c r="D84" s="44">
         <v>44381</v>
       </c>
-      <c r="E84" s="45">
+      <c r="E84" s="4">
         <v>41</v>
       </c>
     </row>
@@ -5769,7 +5759,7 @@
       <c r="D85" s="44">
         <v>44381</v>
       </c>
-      <c r="E85" s="45">
+      <c r="E85" s="4">
         <v>23</v>
       </c>
     </row>
@@ -5786,7 +5776,7 @@
       <c r="D86" s="44">
         <v>44381</v>
       </c>
-      <c r="E86" s="45">
+      <c r="E86" s="4">
         <v>17</v>
       </c>
     </row>
@@ -5803,7 +5793,7 @@
       <c r="D87" s="44">
         <v>44382</v>
       </c>
-      <c r="E87" s="45">
+      <c r="E87" s="4">
         <v>92</v>
       </c>
     </row>
@@ -5820,7 +5810,7 @@
       <c r="D88" s="44">
         <v>44382</v>
       </c>
-      <c r="E88" s="45">
+      <c r="E88" s="4">
         <v>73</v>
       </c>
     </row>
@@ -5837,7 +5827,7 @@
       <c r="D89" s="44">
         <v>44378</v>
       </c>
-      <c r="E89" s="45">
+      <c r="E89" s="4">
         <v>12</v>
       </c>
     </row>
@@ -5854,7 +5844,7 @@
       <c r="D90" s="44">
         <v>44379</v>
       </c>
-      <c r="E90" s="45">
+      <c r="E90" s="4">
         <v>96</v>
       </c>
     </row>
@@ -5871,7 +5861,7 @@
       <c r="D91" s="44">
         <v>44378</v>
       </c>
-      <c r="E91" s="45">
+      <c r="E91" s="4">
         <v>38</v>
       </c>
     </row>
@@ -5882,13 +5872,13 @@
       <c r="B92" s="43" t="s">
         <v>309</v>
       </c>
-      <c r="C92" s="46" t="s">
+      <c r="C92" s="45" t="s">
         <v>310</v>
       </c>
       <c r="D92" s="44">
         <v>44378</v>
       </c>
-      <c r="E92" s="45">
+      <c r="E92" s="4">
         <v>98</v>
       </c>
     </row>
@@ -5905,7 +5895,7 @@
       <c r="D93" s="44">
         <v>44378</v>
       </c>
-      <c r="E93" s="45">
+      <c r="E93" s="4">
         <v>84</v>
       </c>
     </row>
@@ -5922,7 +5912,7 @@
       <c r="D94" s="44">
         <v>44379</v>
       </c>
-      <c r="E94" s="45">
+      <c r="E94" s="4">
         <v>81</v>
       </c>
     </row>
@@ -5939,7 +5929,7 @@
       <c r="D95" s="44">
         <v>44379</v>
       </c>
-      <c r="E95" s="45">
+      <c r="E95" s="4">
         <v>51</v>
       </c>
     </row>
@@ -5956,7 +5946,7 @@
       <c r="D96" s="44">
         <v>44379</v>
       </c>
-      <c r="E96" s="45">
+      <c r="E96" s="4">
         <v>91</v>
       </c>
     </row>
@@ -5973,7 +5963,7 @@
       <c r="D97" s="44">
         <v>44378</v>
       </c>
-      <c r="E97" s="45">
+      <c r="E97" s="4">
         <v>66</v>
       </c>
     </row>
@@ -5990,7 +5980,7 @@
       <c r="D98" s="44">
         <v>44379</v>
       </c>
-      <c r="E98" s="45">
+      <c r="E98" s="4">
         <v>85</v>
       </c>
     </row>
@@ -6007,7 +5997,7 @@
       <c r="D99" s="44">
         <v>44378</v>
       </c>
-      <c r="E99" s="45">
+      <c r="E99" s="4">
         <v>14</v>
       </c>
     </row>
@@ -6024,7 +6014,7 @@
       <c r="D100" s="44">
         <v>44379</v>
       </c>
-      <c r="E100" s="45">
+      <c r="E100" s="4">
         <v>56</v>
       </c>
     </row>
@@ -6041,24 +6031,24 @@
       <c r="D101" s="44">
         <v>44379</v>
       </c>
-      <c r="E101" s="45">
+      <c r="E101" s="4">
         <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A102" s="47" t="s">
+      <c r="A102" s="46" t="s">
         <v>338</v>
       </c>
-      <c r="B102" s="47" t="s">
+      <c r="B102" s="46" t="s">
         <v>339</v>
       </c>
-      <c r="C102" s="47" t="s">
+      <c r="C102" s="46" t="s">
         <v>340</v>
       </c>
-      <c r="D102" s="48">
+      <c r="D102" s="47">
         <v>44379</v>
       </c>
-      <c r="E102" s="49">
+      <c r="E102" s="6">
         <v>59</v>
       </c>
     </row>
@@ -6084,45 +6074,45 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="D2" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="86" t="s">
+      <c r="E2" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="86" t="s">
+      <c r="F2" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="86" t="s">
+      <c r="G2" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="86" t="s">
+      <c r="H2" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="87" t="s">
+      <c r="I2" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="88" t="s">
+      <c r="J2" s="81" t="s">
         <v>342</v>
       </c>
-      <c r="L2" s="89" t="s">
+      <c r="L2" s="82" t="s">
         <v>451</v>
       </c>
-      <c r="M2" s="89" t="s">
+      <c r="M2" s="82" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="51" t="s">
         <v>343</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -6134,10 +6124,10 @@
       <c r="D3" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="E3" s="54">
+      <c r="E3" s="52">
         <v>43550</v>
       </c>
-      <c r="F3" s="54">
+      <c r="F3" s="52">
         <v>43916</v>
       </c>
       <c r="G3" s="8" t="s">
@@ -6146,21 +6136,21 @@
       <c r="H3" s="7">
         <v>8329</v>
       </c>
-      <c r="I3" s="55" t="s">
+      <c r="I3" s="53" t="s">
         <v>348</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="L3" s="58" t="s">
+      <c r="L3" s="56" t="s">
         <v>453</v>
       </c>
-      <c r="M3" s="58" t="s">
+      <c r="M3" s="56" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="51" t="s">
         <v>350</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -6172,10 +6162,10 @@
       <c r="D4" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="E4" s="54">
+      <c r="E4" s="52">
         <v>43535</v>
       </c>
-      <c r="F4" s="54">
+      <c r="F4" s="52">
         <v>43901</v>
       </c>
       <c r="G4" s="8" t="s">
@@ -6184,21 +6174,21 @@
       <c r="H4" s="7">
         <v>4778</v>
       </c>
-      <c r="I4" s="53" t="s">
+      <c r="I4" s="51" t="s">
         <v>355</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="L4" s="59" t="s">
+      <c r="L4" s="57" t="s">
         <v>455</v>
       </c>
-      <c r="M4" s="59" t="s">
+      <c r="M4" s="57" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="51" t="s">
         <v>357</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -6210,10 +6200,10 @@
       <c r="D5" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="E5" s="54">
+      <c r="E5" s="52">
         <v>43500</v>
       </c>
-      <c r="F5" s="54">
+      <c r="F5" s="52">
         <v>43865</v>
       </c>
       <c r="G5" s="8" t="s">
@@ -6222,21 +6212,21 @@
       <c r="H5" s="7">
         <v>5412</v>
       </c>
-      <c r="I5" s="53" t="s">
+      <c r="I5" s="51" t="s">
         <v>348</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="L5" s="59" t="s">
+      <c r="L5" s="57" t="s">
         <v>457</v>
       </c>
-      <c r="M5" s="59" t="s">
+      <c r="M5" s="57" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="51" t="s">
         <v>362</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -6248,10 +6238,10 @@
       <c r="D6" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="52">
         <v>43432</v>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="52">
         <v>43797</v>
       </c>
       <c r="G6" s="8" t="s">
@@ -6260,17 +6250,17 @@
       <c r="H6" s="7">
         <v>1235</v>
       </c>
-      <c r="I6" s="53" t="s">
+      <c r="I6" s="51" t="s">
         <v>355</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="L6" s="60"/>
+      <c r="L6" s="50"/>
       <c r="M6" s="6"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="51" t="s">
         <v>367</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -6282,10 +6272,10 @@
       <c r="D7" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="E7" s="54">
+      <c r="E7" s="52">
         <v>43446</v>
       </c>
-      <c r="F7" s="54">
+      <c r="F7" s="52">
         <v>43811</v>
       </c>
       <c r="G7" s="8" t="s">
@@ -6294,7 +6284,7 @@
       <c r="H7" s="7">
         <v>5543</v>
       </c>
-      <c r="I7" s="53" t="s">
+      <c r="I7" s="51" t="s">
         <v>355</v>
       </c>
       <c r="J7" s="8" t="s">
@@ -6302,7 +6292,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="51" t="s">
         <v>371</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -6314,10 +6304,10 @@
       <c r="D8" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="E8" s="54">
+      <c r="E8" s="52">
         <v>43608</v>
       </c>
-      <c r="F8" s="54">
+      <c r="F8" s="52">
         <v>43792</v>
       </c>
       <c r="G8" s="8" t="s">
@@ -6326,7 +6316,7 @@
       <c r="H8" s="7">
         <v>9023</v>
       </c>
-      <c r="I8" s="53" t="s">
+      <c r="I8" s="51" t="s">
         <v>348</v>
       </c>
       <c r="J8" s="8" t="s">
@@ -6334,7 +6324,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="51" t="s">
         <v>376</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -6346,10 +6336,10 @@
       <c r="D9" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="E9" s="54">
+      <c r="E9" s="52">
         <v>43554</v>
       </c>
-      <c r="F9" s="54">
+      <c r="F9" s="52">
         <v>43738</v>
       </c>
       <c r="G9" s="8" t="s">
@@ -6358,7 +6348,7 @@
       <c r="H9" s="7">
         <v>6653</v>
       </c>
-      <c r="I9" s="53" t="s">
+      <c r="I9" s="51" t="s">
         <v>355</v>
       </c>
       <c r="J9" s="8" t="s">
@@ -6366,7 +6356,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="51" t="s">
         <v>381</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -6378,10 +6368,10 @@
       <c r="D10" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="E10" s="54">
+      <c r="E10" s="52">
         <v>43638</v>
       </c>
-      <c r="F10" s="54">
+      <c r="F10" s="52">
         <v>43821</v>
       </c>
       <c r="G10" s="8" t="s">
@@ -6390,7 +6380,7 @@
       <c r="H10" s="7">
         <v>5919</v>
       </c>
-      <c r="I10" s="53" t="s">
+      <c r="I10" s="51" t="s">
         <v>355</v>
       </c>
       <c r="J10" s="8" t="s">
@@ -6398,7 +6388,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11" s="53" t="s">
+      <c r="A11" s="51" t="s">
         <v>385</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -6410,10 +6400,10 @@
       <c r="D11" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="E11" s="54">
+      <c r="E11" s="52">
         <v>43366</v>
       </c>
-      <c r="F11" s="54">
+      <c r="F11" s="52">
         <v>43913</v>
       </c>
       <c r="G11" s="8" t="s">
@@ -6422,7 +6412,7 @@
       <c r="H11" s="7">
         <v>5622</v>
       </c>
-      <c r="I11" s="53" t="s">
+      <c r="I11" s="51" t="s">
         <v>390</v>
       </c>
       <c r="J11" s="8" t="s">
@@ -6430,7 +6420,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="51" t="s">
         <v>392</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -6442,10 +6432,10 @@
       <c r="D12" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="E12" s="54">
+      <c r="E12" s="52">
         <v>43724</v>
       </c>
-      <c r="F12" s="54">
+      <c r="F12" s="52">
         <v>43906</v>
       </c>
       <c r="G12" s="8" t="s">
@@ -6454,7 +6444,7 @@
       <c r="H12" s="7">
         <v>3367</v>
       </c>
-      <c r="I12" s="53" t="s">
+      <c r="I12" s="51" t="s">
         <v>396</v>
       </c>
       <c r="J12" s="8" t="s">
@@ -6462,7 +6452,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="51" t="s">
         <v>398</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -6474,10 +6464,10 @@
       <c r="D13" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="E13" s="54">
+      <c r="E13" s="52">
         <v>43387</v>
       </c>
-      <c r="F13" s="54">
+      <c r="F13" s="52">
         <v>43752</v>
       </c>
       <c r="G13" s="8" t="s">
@@ -6486,7 +6476,7 @@
       <c r="H13" s="7">
         <v>1768</v>
       </c>
-      <c r="I13" s="53" t="s">
+      <c r="I13" s="51" t="s">
         <v>396</v>
       </c>
       <c r="J13" s="8" t="s">
@@ -6494,7 +6484,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="51" t="s">
         <v>402</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -6506,10 +6496,10 @@
       <c r="D14" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="E14" s="54">
+      <c r="E14" s="52">
         <v>43572</v>
       </c>
-      <c r="F14" s="54">
+      <c r="F14" s="52">
         <v>43938</v>
       </c>
       <c r="G14" s="8" t="s">
@@ -6518,7 +6508,7 @@
       <c r="H14" s="7">
         <v>1947</v>
       </c>
-      <c r="I14" s="53" t="s">
+      <c r="I14" s="51" t="s">
         <v>390</v>
       </c>
       <c r="J14" s="8" t="s">
@@ -6526,7 +6516,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A15" s="53" t="s">
+      <c r="A15" s="51" t="s">
         <v>406</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -6538,10 +6528,10 @@
       <c r="D15" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="E15" s="54">
+      <c r="E15" s="52">
         <v>43661</v>
       </c>
-      <c r="F15" s="54">
+      <c r="F15" s="52">
         <v>43845</v>
       </c>
       <c r="G15" s="8" t="s">
@@ -6550,7 +6540,7 @@
       <c r="H15" s="7">
         <v>4999</v>
       </c>
-      <c r="I15" s="53" t="s">
+      <c r="I15" s="51" t="s">
         <v>348</v>
       </c>
       <c r="J15" s="8" t="s">
@@ -6558,7 +6548,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A16" s="53" t="s">
+      <c r="A16" s="51" t="s">
         <v>410</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -6570,10 +6560,10 @@
       <c r="D16" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="E16" s="54">
+      <c r="E16" s="52">
         <v>43687</v>
       </c>
-      <c r="F16" s="54">
+      <c r="F16" s="52">
         <v>44053</v>
       </c>
       <c r="G16" s="8" t="s">
@@ -6582,7 +6572,7 @@
       <c r="H16" s="7">
         <v>5553</v>
       </c>
-      <c r="I16" s="53" t="s">
+      <c r="I16" s="51" t="s">
         <v>348</v>
       </c>
       <c r="J16" s="8" t="s">
@@ -6590,7 +6580,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="53" t="s">
+      <c r="A17" s="51" t="s">
         <v>413</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -6602,10 +6592,10 @@
       <c r="D17" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="E17" s="54">
+      <c r="E17" s="52">
         <v>43688</v>
       </c>
-      <c r="F17" s="54">
+      <c r="F17" s="52">
         <v>43872</v>
       </c>
       <c r="G17" s="8" t="s">
@@ -6614,7 +6604,7 @@
       <c r="H17" s="7">
         <v>2473</v>
       </c>
-      <c r="I17" s="53" t="s">
+      <c r="I17" s="51" t="s">
         <v>390</v>
       </c>
       <c r="J17" s="8" t="s">
@@ -6622,7 +6612,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="51" t="s">
         <v>416</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -6634,10 +6624,10 @@
       <c r="D18" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="E18" s="54">
+      <c r="E18" s="52">
         <v>43553</v>
       </c>
-      <c r="F18" s="54">
+      <c r="F18" s="52">
         <v>43737</v>
       </c>
       <c r="G18" s="8" t="s">
@@ -6646,7 +6636,7 @@
       <c r="H18" s="7">
         <v>1994</v>
       </c>
-      <c r="I18" s="53" t="s">
+      <c r="I18" s="51" t="s">
         <v>396</v>
       </c>
       <c r="J18" s="8" t="s">
@@ -6654,7 +6644,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A19" s="53" t="s">
+      <c r="A19" s="51" t="s">
         <v>419</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -6666,10 +6656,10 @@
       <c r="D19" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="E19" s="54">
+      <c r="E19" s="52">
         <v>43389</v>
       </c>
-      <c r="F19" s="54">
+      <c r="F19" s="52">
         <v>43937</v>
       </c>
       <c r="G19" s="8" t="s">
@@ -6678,7 +6668,7 @@
       <c r="H19" s="7">
         <v>1225</v>
       </c>
-      <c r="I19" s="53" t="s">
+      <c r="I19" s="51" t="s">
         <v>396</v>
       </c>
       <c r="J19" s="8" t="s">
@@ -6686,7 +6676,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="53" t="s">
+      <c r="A20" s="51" t="s">
         <v>422</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -6698,10 +6688,10 @@
       <c r="D20" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="E20" s="54">
+      <c r="E20" s="52">
         <v>43647</v>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="52">
         <v>44013</v>
       </c>
       <c r="G20" s="8" t="s">
@@ -6710,7 +6700,7 @@
       <c r="H20" s="7">
         <v>1705</v>
       </c>
-      <c r="I20" s="53" t="s">
+      <c r="I20" s="51" t="s">
         <v>355</v>
       </c>
       <c r="J20" s="8" t="s">
@@ -6718,7 +6708,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A21" s="53" t="s">
+      <c r="A21" s="51" t="s">
         <v>425</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -6730,10 +6720,10 @@
       <c r="D21" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="E21" s="54">
+      <c r="E21" s="52">
         <v>43528</v>
       </c>
-      <c r="F21" s="54">
+      <c r="F21" s="52">
         <v>43894</v>
       </c>
       <c r="G21" s="8" t="s">
@@ -6742,7 +6732,7 @@
       <c r="H21" s="7">
         <v>3098</v>
       </c>
-      <c r="I21" s="53" t="s">
+      <c r="I21" s="51" t="s">
         <v>348</v>
       </c>
       <c r="J21" s="8" t="s">
@@ -6750,7 +6740,7 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="51" t="s">
         <v>430</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -6762,10 +6752,10 @@
       <c r="D22" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="E22" s="54">
+      <c r="E22" s="52">
         <v>43476</v>
       </c>
-      <c r="F22" s="54">
+      <c r="F22" s="52">
         <v>43841</v>
       </c>
       <c r="G22" s="8" t="s">
@@ -6774,7 +6764,7 @@
       <c r="H22" s="7">
         <v>2678</v>
       </c>
-      <c r="I22" s="53" t="s">
+      <c r="I22" s="51" t="s">
         <v>348</v>
       </c>
       <c r="J22" s="8" t="s">
@@ -6782,7 +6772,7 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="53" t="s">
+      <c r="A23" s="51" t="s">
         <v>434</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -6794,10 +6784,10 @@
       <c r="D23" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="E23" s="54">
+      <c r="E23" s="52">
         <v>43479</v>
       </c>
-      <c r="F23" s="54">
+      <c r="F23" s="52">
         <v>43844</v>
       </c>
       <c r="G23" s="8" t="s">
@@ -6806,7 +6796,7 @@
       <c r="H23" s="7">
         <v>2234</v>
       </c>
-      <c r="I23" s="53" t="s">
+      <c r="I23" s="51" t="s">
         <v>348</v>
       </c>
       <c r="J23" s="8" t="s">
@@ -6814,7 +6804,7 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="51" t="s">
         <v>437</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -6826,10 +6816,10 @@
       <c r="D24" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="E24" s="54">
+      <c r="E24" s="52">
         <v>43602</v>
       </c>
-      <c r="F24" s="54">
+      <c r="F24" s="52">
         <v>43968</v>
       </c>
       <c r="G24" s="8" t="s">
@@ -6838,7 +6828,7 @@
       <c r="H24" s="7">
         <v>3786</v>
       </c>
-      <c r="I24" s="53" t="s">
+      <c r="I24" s="51" t="s">
         <v>348</v>
       </c>
       <c r="J24" s="8" t="s">
@@ -6846,7 +6836,7 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="53" t="s">
+      <c r="A25" s="51" t="s">
         <v>441</v>
       </c>
       <c r="B25" s="8" t="s">
@@ -6858,10 +6848,10 @@
       <c r="D25" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="E25" s="54">
+      <c r="E25" s="52">
         <v>43409</v>
       </c>
-      <c r="F25" s="54">
+      <c r="F25" s="52">
         <v>43774</v>
       </c>
       <c r="G25" s="8" t="s">
@@ -6870,7 +6860,7 @@
       <c r="H25" s="7">
         <v>3213</v>
       </c>
-      <c r="I25" s="53" t="s">
+      <c r="I25" s="51" t="s">
         <v>355</v>
       </c>
       <c r="J25" s="8" t="s">
@@ -6878,7 +6868,7 @@
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="54" t="s">
         <v>446</v>
       </c>
       <c r="B26" s="10" t="s">
@@ -6890,10 +6880,10 @@
       <c r="D26" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="E26" s="57">
+      <c r="E26" s="55">
         <v>43515</v>
       </c>
-      <c r="F26" s="57">
+      <c r="F26" s="55">
         <v>43880</v>
       </c>
       <c r="G26" s="10" t="s">
@@ -6902,7 +6892,7 @@
       <c r="H26" s="9">
         <v>1135</v>
       </c>
-      <c r="I26" s="56" t="s">
+      <c r="I26" s="54" t="s">
         <v>348</v>
       </c>
       <c r="J26" s="10" t="s">
@@ -6924,7 +6914,6 @@
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="68"/>
     <col min="7" max="7" width="32.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -6935,532 +6924,532 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="83" t="s">
         <v>459</v>
       </c>
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="83" t="s">
         <v>460</v>
       </c>
-      <c r="C2" s="90" t="s">
+      <c r="C2" s="83" t="s">
         <v>461</v>
       </c>
-      <c r="D2" s="90" t="s">
+      <c r="D2" s="83" t="s">
         <v>462</v>
       </c>
-      <c r="E2" s="90" t="s">
+      <c r="E2" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="90" t="s">
+      <c r="F2" s="61"/>
+      <c r="G2" s="83" t="s">
         <v>463</v>
       </c>
-      <c r="H2" s="90" t="s">
+      <c r="H2" s="83" t="s">
         <v>464</v>
       </c>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="69">
+      <c r="A3" s="62">
         <v>1</v>
       </c>
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="62" t="s">
         <v>465</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="63" t="s">
         <v>466</v>
       </c>
-      <c r="D3" s="69">
+      <c r="D3" s="62">
         <v>55000</v>
       </c>
-      <c r="E3" s="69"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="69" t="s">
+      <c r="E3" s="62"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="62" t="s">
         <v>467</v>
       </c>
-      <c r="H3" s="70">
+      <c r="H3" s="63">
         <v>0.8</v>
       </c>
-      <c r="I3" s="61"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="61"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="69">
+      <c r="A4" s="62">
         <v>2</v>
       </c>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="62" t="s">
         <v>468</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="63" t="s">
         <v>467</v>
       </c>
-      <c r="D4" s="69">
+      <c r="D4" s="62">
         <v>42000</v>
       </c>
-      <c r="E4" s="69"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="69" t="s">
+      <c r="E4" s="62"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="62" t="s">
         <v>466</v>
       </c>
-      <c r="H4" s="70">
+      <c r="H4" s="63">
         <v>0.6</v>
       </c>
-      <c r="I4" s="61"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="69">
+      <c r="A5" s="62">
         <v>3</v>
       </c>
-      <c r="B5" s="69" t="s">
+      <c r="B5" s="62" t="s">
         <v>469</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="63" t="s">
         <v>466</v>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="62">
         <v>45000</v>
       </c>
-      <c r="E5" s="69"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="69" t="s">
+      <c r="E5" s="62"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="62" t="s">
         <v>470</v>
       </c>
-      <c r="H5" s="70">
+      <c r="H5" s="63">
         <v>0.4</v>
       </c>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="69">
+      <c r="A6" s="62">
         <v>4</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="62" t="s">
         <v>471</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="63" t="s">
         <v>472</v>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="62">
         <v>65000</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="71" t="s">
+      <c r="E6" s="62"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="64" t="s">
         <v>473</v>
       </c>
-      <c r="H6" s="72" t="s">
+      <c r="H6" s="65" t="s">
         <v>474</v>
       </c>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="61"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="69">
+      <c r="A7" s="62">
         <v>5</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="62" t="s">
         <v>475</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="63" t="s">
         <v>473</v>
       </c>
-      <c r="D7" s="69">
+      <c r="D7" s="62">
         <v>70000</v>
       </c>
-      <c r="E7" s="69"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="61"/>
-      <c r="K7" s="61"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="69">
+      <c r="A8" s="62">
         <v>6</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="62" t="s">
         <v>476</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="63" t="s">
         <v>470</v>
       </c>
-      <c r="D8" s="69">
+      <c r="D8" s="62">
         <v>75000</v>
       </c>
-      <c r="E8" s="69"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="J8" s="61"/>
-      <c r="K8" s="61"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="69">
+      <c r="A9" s="62">
         <v>7</v>
       </c>
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="62" t="s">
         <v>478</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="63" t="s">
         <v>467</v>
       </c>
-      <c r="D9" s="69">
+      <c r="D9" s="62">
         <v>33000</v>
       </c>
-      <c r="E9" s="69"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="69">
+      <c r="A10" s="62">
         <v>8</v>
       </c>
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="62" t="s">
         <v>479</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="63" t="s">
         <v>470</v>
       </c>
-      <c r="D10" s="69">
+      <c r="D10" s="62">
         <v>45000</v>
       </c>
-      <c r="E10" s="69"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="73" t="s">
+      <c r="E10" s="62"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="66" t="s">
         <v>477</v>
       </c>
-      <c r="H10" s="93"/>
-      <c r="J10" s="61"/>
-      <c r="K10" s="61"/>
+      <c r="H10" s="86"/>
+      <c r="J10" s="58"/>
+      <c r="K10" s="58"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="69">
+      <c r="A11" s="62">
         <v>9</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="62" t="s">
         <v>480</v>
       </c>
-      <c r="C11" s="70" t="s">
+      <c r="C11" s="63" t="s">
         <v>481</v>
       </c>
-      <c r="D11" s="69">
+      <c r="D11" s="62">
         <v>50000</v>
       </c>
-      <c r="E11" s="69"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="74" t="s">
+      <c r="E11" s="62"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="67" t="s">
         <v>482</v>
       </c>
-      <c r="H11" s="94"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
+      <c r="H11" s="87"/>
+      <c r="J11" s="58"/>
+      <c r="K11" s="58"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="69">
+      <c r="A12" s="62">
         <v>10</v>
       </c>
-      <c r="B12" s="69" t="s">
+      <c r="B12" s="62" t="s">
         <v>483</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="63" t="s">
         <v>470</v>
       </c>
-      <c r="D12" s="69">
+      <c r="D12" s="62">
         <v>60000</v>
       </c>
-      <c r="E12" s="69"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="74" t="s">
+      <c r="E12" s="62"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="67" t="s">
         <v>486</v>
       </c>
-      <c r="H12" s="95"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
+      <c r="H12" s="88"/>
+      <c r="J12" s="58"/>
+      <c r="K12" s="58"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="69">
+      <c r="A13" s="62">
         <v>11</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="62" t="s">
         <v>484</v>
       </c>
-      <c r="C13" s="70" t="s">
+      <c r="C13" s="63" t="s">
         <v>466</v>
       </c>
-      <c r="D13" s="69">
+      <c r="D13" s="62">
         <v>48000</v>
       </c>
-      <c r="E13" s="69"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="75" t="s">
+      <c r="E13" s="62"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="68" t="s">
         <v>490</v>
       </c>
-      <c r="H13" s="94"/>
-      <c r="J13" s="61"/>
-      <c r="K13" s="61"/>
+      <c r="H13" s="87"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="58"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="69">
+      <c r="A14" s="62">
         <v>12</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="62" t="s">
         <v>485</v>
       </c>
-      <c r="C14" s="70" t="s">
+      <c r="C14" s="63" t="s">
         <v>467</v>
       </c>
-      <c r="D14" s="69">
+      <c r="D14" s="62">
         <v>35000</v>
       </c>
-      <c r="E14" s="69"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="91" t="s">
+      <c r="E14" s="62"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="84" t="s">
         <v>478</v>
       </c>
-      <c r="H14" s="94"/>
-      <c r="J14" s="61"/>
-      <c r="K14" s="61"/>
+      <c r="H14" s="87"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="58"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="69">
+      <c r="A15" s="62">
         <v>13</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="62" t="s">
         <v>487</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="63" t="s">
         <v>470</v>
       </c>
-      <c r="D15" s="69">
+      <c r="D15" s="62">
         <v>40000</v>
       </c>
-      <c r="E15" s="69"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="92" t="s">
+      <c r="E15" s="62"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="85" t="s">
         <v>467</v>
       </c>
-      <c r="H15" s="96"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
+      <c r="H15" s="89"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="58"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="69">
+      <c r="A16" s="62">
         <v>14</v>
       </c>
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="62" t="s">
         <v>488</v>
       </c>
-      <c r="C16" s="70" t="s">
+      <c r="C16" s="63" t="s">
         <v>481</v>
       </c>
-      <c r="D16" s="69">
+      <c r="D16" s="62">
         <v>55000</v>
       </c>
-      <c r="E16" s="69"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="69">
+      <c r="A17" s="62">
         <v>15</v>
       </c>
-      <c r="B17" s="69" t="s">
+      <c r="B17" s="62" t="s">
         <v>489</v>
       </c>
-      <c r="C17" s="70" t="s">
+      <c r="C17" s="63" t="s">
         <v>466</v>
       </c>
-      <c r="D17" s="69">
+      <c r="D17" s="62">
         <v>36000</v>
       </c>
-      <c r="E17" s="69"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="61"/>
-      <c r="J17" s="62"/>
-      <c r="K17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="J17" s="59"/>
+      <c r="K17" s="59"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="69">
+      <c r="A18" s="62">
         <v>16</v>
       </c>
-      <c r="B18" s="69" t="s">
+      <c r="B18" s="62" t="s">
         <v>491</v>
       </c>
-      <c r="C18" s="70" t="s">
+      <c r="C18" s="63" t="s">
         <v>473</v>
       </c>
-      <c r="D18" s="69">
+      <c r="D18" s="62">
         <v>58000</v>
       </c>
-      <c r="E18" s="69"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="66"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="7"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="58"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="69">
+      <c r="A19" s="62">
         <v>17</v>
       </c>
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="62" t="s">
         <v>492</v>
       </c>
-      <c r="C19" s="70" t="s">
+      <c r="C19" s="63" t="s">
         <v>466</v>
       </c>
-      <c r="D19" s="69">
+      <c r="D19" s="62">
         <v>49000</v>
       </c>
-      <c r="E19" s="69"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="69">
+      <c r="A20" s="62">
         <v>18</v>
       </c>
-      <c r="B20" s="69" t="s">
+      <c r="B20" s="62" t="s">
         <v>493</v>
       </c>
-      <c r="C20" s="70" t="s">
+      <c r="C20" s="63" t="s">
         <v>466</v>
       </c>
-      <c r="D20" s="69">
+      <c r="D20" s="62">
         <v>55000</v>
       </c>
-      <c r="E20" s="69"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="69">
+      <c r="A21" s="62">
         <v>19</v>
       </c>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="62" t="s">
         <v>494</v>
       </c>
-      <c r="C21" s="70" t="s">
+      <c r="C21" s="63" t="s">
         <v>473</v>
       </c>
-      <c r="D21" s="69">
+      <c r="D21" s="62">
         <v>66000</v>
       </c>
-      <c r="E21" s="69"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="61"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="58"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="69">
+      <c r="A22" s="62">
         <v>20</v>
       </c>
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="62" t="s">
         <v>495</v>
       </c>
-      <c r="C22" s="70" t="s">
+      <c r="C22" s="63" t="s">
         <v>470</v>
       </c>
-      <c r="D22" s="69">
+      <c r="D22" s="62">
         <v>52000</v>
       </c>
-      <c r="E22" s="69"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="61"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="58"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="69">
+      <c r="A23" s="62">
         <v>21</v>
       </c>
-      <c r="B23" s="69" t="s">
+      <c r="B23" s="62" t="s">
         <v>496</v>
       </c>
-      <c r="C23" s="70" t="s">
+      <c r="C23" s="63" t="s">
         <v>470</v>
       </c>
-      <c r="D23" s="69">
+      <c r="D23" s="62">
         <v>44000</v>
       </c>
-      <c r="E23" s="69"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="61"/>
-      <c r="K23" s="61"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="69">
+      <c r="A24" s="62">
         <v>22</v>
       </c>
-      <c r="B24" s="69" t="s">
+      <c r="B24" s="62" t="s">
         <v>497</v>
       </c>
-      <c r="C24" s="70" t="s">
+      <c r="C24" s="63" t="s">
         <v>466</v>
       </c>
-      <c r="D24" s="69">
+      <c r="D24" s="62">
         <v>30000</v>
       </c>
-      <c r="E24" s="69"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="61"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="58"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="71">
+      <c r="A25" s="64">
         <v>23</v>
       </c>
-      <c r="B25" s="71" t="s">
+      <c r="B25" s="64" t="s">
         <v>498</v>
       </c>
-      <c r="C25" s="72" t="s">
+      <c r="C25" s="65" t="s">
         <v>466</v>
       </c>
-      <c r="D25" s="71">
+      <c r="D25" s="64">
         <v>54000</v>
       </c>
-      <c r="E25" s="71"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="61"/>
+      <c r="E25" s="64"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
